--- a/src/main/resources/config/PriceGuideData.xlsx
+++ b/src/main/resources/config/PriceGuideData.xlsx
@@ -30,157 +30,157 @@
     <x:t>Item_Name</x:t>
   </x:si>
   <x:si>
+    <x:t>카테고리별 아이템 갯수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일반이불</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,500</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거위털이불</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오리털이불</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,800</x:t>
+  </x:si>
+  <x:si>
+    <x:t>면(티셔츠)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>50,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>극세사이불</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10,900</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5,500</x:t>
+  </x:si>
+  <x:si>
+    <x:t>니트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>의류</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로퍼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신발</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가디건</x:t>
+  </x:si>
+  <x:si>
+    <x:t>침구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>리빙</x:t>
+  </x:si>
+  <x:si>
+    <x:t>점퍼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목도리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스웨터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>러그</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가죽</x:t>
+  </x:si>
+  <x:si>
     <x:t>모자</x:t>
   </x:si>
   <x:si>
-    <x:t>로퍼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가죽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목도리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인형</x:t>
-  </x:si>
-  <x:si>
     <x:t>원피스</x:t>
   </x:si>
   <x:si>
-    <x:t>신발</x:t>
-  </x:si>
-  <x:si>
-    <x:t>의류</x:t>
-  </x:si>
-  <x:si>
-    <x:t>니트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가디건</x:t>
-  </x:si>
-  <x:si>
-    <x:t>침구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>리빙</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스웨터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>점퍼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>러그</x:t>
+    <x:t>맨투맨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>후드티</x:t>
+  </x:si>
+  <x:si>
+    <x:t>커튼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스커트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자켓</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스카프</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>운동화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구두</x:t>
+  </x:si>
+  <x:si>
+    <x:t>셔츠</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카페트</x:t>
   </x:si>
   <x:si>
     <x:t>패딩</x:t>
   </x:si>
   <x:si>
-    <x:t>셔츠</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스카프</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스커트</x:t>
-  </x:si>
-  <x:si>
     <x:t>장갑</x:t>
   </x:si>
   <x:si>
-    <x:t>구두</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카페트</x:t>
-  </x:si>
-  <x:si>
     <x:t>부츠</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맨투맨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>후드티</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자켓</x:t>
-  </x:si>
-  <x:si>
-    <x:t>바지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>커튼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>운동화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카테고리별 아이템 갯수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>면(티셔츠)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>50,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3,500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일반이불</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거위털이불</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오리털이불</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1,800</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10,900</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5,500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>극세사이불</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5,000</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1088,42 +1088,42 @@
     </x:row>
     <x:row r="2" spans="1:3" ht="17.800000000000001">
       <x:c r="A2" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B2" s="5" t="s">
-        <x:v>19</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C2" s="8" t="s">
-        <x:v>43</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" ht="17.800000000000001" customHeight="1">
       <x:c r="A3" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B3" s="5" t="s">
-        <x:v>35</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C3" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G3" s="11" t="s">
-        <x:v>33</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H3" s="11"/>
     </x:row>
     <x:row r="4" spans="1:8" ht="17.800000000000001">
       <x:c r="A4" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
-        <x:v>27</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C4" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G4" s="9" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H4" s="10">
         <x:f>COUNTIF(A:A,"의류")</x:f>
@@ -1132,16 +1132,16 @@
     </x:row>
     <x:row r="5" spans="1:8" ht="17.800000000000001">
       <x:c r="A5" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>28</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C5" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G5" s="10" t="s">
-        <x:v>13</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H5" s="10">
         <x:f>COUNTIF(A:A,"침구")</x:f>
@@ -1150,16 +1150,16 @@
     </x:row>
     <x:row r="6" spans="1:8" ht="17.800000000000001">
       <x:c r="A6" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C6" s="8" t="s">
-        <x:v>53</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G6" s="10" t="s">
-        <x:v>9</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H6" s="10">
         <x:f>COUNTIF(A:A,"신발")</x:f>
@@ -1168,16 +1168,16 @@
     </x:row>
     <x:row r="7" spans="1:8" ht="17.800000000000001">
       <x:c r="A7" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>15</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C7" s="8" t="s">
-        <x:v>53</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G7" s="10" t="s">
-        <x:v>14</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H7" s="10">
         <x:f>COUNTIF(A:A,"리빙")</x:f>
@@ -1186,284 +1186,284 @@
     </x:row>
     <x:row r="8" spans="1:3" ht="17.800000000000001">
       <x:c r="A8" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>12</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C8" s="8" t="s">
-        <x:v>53</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3" ht="17.800000000000001">
       <x:c r="A9" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C9" s="8" t="s">
-        <x:v>53</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3" ht="17.800000000000001">
       <x:c r="A10" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B10" s="5" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C10" s="8" t="s">
         <x:v>16</x:v>
-      </x:c>
-      <x:c r="C10" s="8" t="s">
-        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3" ht="17.800000000000001">
       <x:c r="A11" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B11" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C11" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3" ht="17.800000000000001">
       <x:c r="A12" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B12" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C12" s="8" t="s">
-        <x:v>47</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3" ht="17.800000000000001">
       <x:c r="A13" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B13" s="5" t="s">
-        <x:v>30</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C13" s="8" t="s">
-        <x:v>39</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3" ht="17.800000000000001">
       <x:c r="A14" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B14" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C14" s="8" t="s">
-        <x:v>39</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3" ht="17.800000000000001">
       <x:c r="A15" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B15" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C15" s="8" t="s">
-        <x:v>45</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3" ht="17.800000000000001">
       <x:c r="A16" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B16" s="5" t="s">
-        <x:v>6</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C16" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3" ht="17.800000000000001">
       <x:c r="A17" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B17" s="5" t="s">
-        <x:v>20</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C17" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3" ht="17.800000000000001">
       <x:c r="A18" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B18" s="5" t="s">
-        <x:v>22</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C18" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3" ht="17.800000000000001">
       <x:c r="A19" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="5" t="s">
-        <x:v>26</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C19" s="8" t="s">
-        <x:v>44</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3" ht="17.800000000000001">
       <x:c r="A20" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B20" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C20" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3" ht="17.800000000000001">
       <x:c r="A21" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B21" s="5" t="s">
-        <x:v>40</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C21" s="8" t="s">
-        <x:v>44</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3" ht="17.800000000000001">
       <x:c r="A22" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B22" s="5" t="s">
-        <x:v>52</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C22" s="8" t="s">
-        <x:v>51</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3" ht="17.800000000000001">
       <x:c r="A23" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B23" s="5" t="s">
-        <x:v>42</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C23" s="8" t="s">
-        <x:v>48</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3" ht="17.800000000000001">
       <x:c r="A24" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="5" t="s">
-        <x:v>41</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C24" s="8" t="s">
-        <x:v>48</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3" ht="17.800000000000001">
       <x:c r="A25" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B25" s="5" t="s">
-        <x:v>32</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C25" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3" ht="17.800000000000001">
       <x:c r="A26" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B26" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C26" s="8" t="s">
-        <x:v>34</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3" ht="17.800000000000001">
       <x:c r="A27" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B27" s="5" t="s">
-        <x:v>4</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C27" s="8" t="s">
-        <x:v>34</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3" ht="17.800000000000001">
       <x:c r="A28" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B28" s="5" t="s">
-        <x:v>25</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C28" s="8" t="s">
-        <x:v>38</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3" ht="17.800000000000001">
       <x:c r="A29" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B29" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C29" s="8" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3" ht="17.800000000000001">
       <x:c r="A30" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B30" s="5" t="s">
-        <x:v>17</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C30" s="8" t="s">
-        <x:v>46</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3" ht="17.800000000000001">
       <x:c r="A31" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B31" s="5" t="s">
-        <x:v>31</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C31" s="8" t="s">
-        <x:v>38</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3" ht="17.800000000000001">
       <x:c r="A32" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C32" s="8" t="s">
-        <x:v>34</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells count="1">
     <x:mergeCell ref="G3:H3"/>
   </x:mergeCells>
-  <x:pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51166665554046631" footer="0.51166665554046631"/>
+  <x:pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51152777671813965" footer="0.51152777671813965"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>